--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId3"/>
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Captura de la línea base · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del §7 y del §13 de la Tesis de Dirección v2.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del §7 y del §13 de la Tesis de Dirección v6.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Captura de la línea base · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del §7 y del §13 de la Tesis de Dirección v6.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del §7 y del §13 de la Tesis de Dirección v7.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Captura de la línea base · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del §7 y del §13 de la Tesis de Dirección v7.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del §7 y del §13 de la Tesis de Dirección v8.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -40,13 +40,13 @@
     <t xml:space="preserve">Captura de la línea base · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del §7 y del §13 de la Tesis de Dirección v8.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 de la Plan de Dirección v8.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>
   </si>
   <si>
-    <t xml:space="preserve">La Tesis declara que el centro no dispone todavía de sus cinco números ni de serie propia en ninguno de los diez indicadores. Este libro es el instrumento para conseguirlos: se rellena una hoja al mes y el resumen anual y el semáforo se calculan solos.</t>
+    <t xml:space="preserve">El Plan de Dirección declara que el centro no dispone todavía de sus cinco números ni de serie propia en ninguno de los diez indicadores. Este libro es el instrumento para conseguirlos: se rellena una hoja al mes y el resumen anual y el semáforo se calculan solos.</t>
   </si>
   <si>
     <t xml:space="preserve">Qué se teclea</t>
@@ -424,7 +424,7 @@
     <t xml:space="preserve">Los cinco números que aún no tenemos</t>
   </si>
   <si>
-    <t xml:space="preserve">§7 de la Tesis. Rellénense las casillas amarillas; los cinco resultados se calculan solos. Hasta que estén, cualquier objetivo comercial es una opinión.</t>
+    <t xml:space="preserve">apartado 7 del Plan de Dirección. Rellénense las casillas amarillas; los cinco resultados se calculan solos. Hasta que estén, cualquier objetivo comercial es una opinión.</t>
   </si>
   <si>
     <t xml:space="preserve">Entradas</t>
@@ -439,13 +439,13 @@
     <t xml:space="preserve">Margen de contribución sobre venta</t>
   </si>
   <si>
-    <t xml:space="preserve">Supuesto de trabajo del §18 mientras no haya escandallo propio.</t>
+    <t xml:space="preserve">Supuesto de trabajo del apartado 18 mientras no haya escandallo propio.</t>
   </si>
   <si>
     <t xml:space="preserve">Ticket medio del caso aceptado</t>
   </si>
   <si>
-    <t xml:space="preserve">Supuesto de trabajo del §18. Se sustituye por el real.</t>
+    <t xml:space="preserve">Supuesto de trabajo del apartado 18. Se sustituye por el real.</t>
   </si>
   <si>
     <t xml:space="preserve">Enlaza con el indicador 6 en cuanto haya tres meses de serie.</t>
@@ -493,7 +493,7 @@
     <t xml:space="preserve">4 · Producto pendiente heredado</t>
   </si>
   <si>
-    <t xml:space="preserve">Caja ya cobrada que hay que convertir en producción. Es la palanca 1 del §14.</t>
+    <t xml:space="preserve">Caja ya cobrada que hay que convertir en producción. Es la palanca 1 del apartado 14.</t>
   </si>
   <si>
     <t xml:space="preserve">5 · Meses de colchón de tesorería</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Captura de la línea base · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 de la Plan de Dirección v8.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v8.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -37,7 +37,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="156">
   <si>
-    <t xml:space="preserve">Captura de la línea base · Centro de Excelencia Implantológica Giraldo</t>
+    <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
     <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v8.0 · Ejercicio 2026</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v8.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v9.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v9.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v10.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v10.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v11.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v11.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v12.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v12.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v13.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v13.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v14.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v14.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v15.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v15.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v16.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v16.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v17.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>

--- a/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
+++ b/instrumentos/Captura-Linea-Base-Giraldo-2026.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Los números del centro · Centro de Excelencia Implantológica Giraldo</t>
   </si>
   <si>
-    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v17.0 · Ejercicio 2026</t>
+    <t xml:space="preserve">Instrumento del apartado 7 y del apartado 13 del Plan de Dirección v18.0 · Ejercicio 2026</t>
   </si>
   <si>
     <t xml:space="preserve">Para qué sirve</t>
